--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.03693</v>
+        <v>16.79681</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62439</v>
+        <v>16.22473</v>
       </c>
       <c r="E2" t="n">
-        <v>16.63047</v>
+        <v>16.62394</v>
       </c>
       <c r="F2" t="n">
-        <v>42.05733</v>
+        <v>42.89228</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05038</v>
+        <v>0.05104</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78989</v>
+        <v>1.84382</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.19134</v>
+        <v>16.94495</v>
       </c>
       <c r="D3" t="n">
-        <v>16.4808</v>
+        <v>16.70768</v>
       </c>
       <c r="E3" t="n">
-        <v>16.84152</v>
+        <v>16.74868</v>
       </c>
       <c r="F3" t="n">
-        <v>43.20436</v>
+        <v>41.71917</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05179</v>
+        <v>0.05104</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82857</v>
+        <v>1.8649</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.84129</v>
+        <v>16.82259</v>
       </c>
       <c r="D4" t="n">
-        <v>16.37691</v>
+        <v>16.79637</v>
       </c>
       <c r="E4" t="n">
-        <v>17.13277</v>
+        <v>16.79715</v>
       </c>
       <c r="F4" t="n">
-        <v>43.3027</v>
+        <v>42.47057</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05059</v>
+        <v>0.05074</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84677</v>
+        <v>1.85529</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.5238</v>
+        <v>17.28213</v>
       </c>
       <c r="D6" t="n">
-        <v>15.63114</v>
+        <v>16.27913</v>
       </c>
       <c r="E6" t="n">
-        <v>16.49141</v>
+        <v>16.45689</v>
       </c>
       <c r="F6" t="n">
-        <v>21.95676</v>
+        <v>21.74762</v>
       </c>
       <c r="G6" t="n">
-        <v>34.506</v>
+        <v>35.24468</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.90166</v>
+        <v>16.55951</v>
       </c>
       <c r="D7" t="n">
-        <v>15.94151</v>
+        <v>15.7342</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7383</v>
+        <v>16.47533</v>
       </c>
       <c r="F7" t="n">
-        <v>21.77061</v>
+        <v>22.0221</v>
       </c>
       <c r="G7" t="n">
-        <v>33.574</v>
+        <v>34.06794</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.8426</v>
+        <v>16.61429</v>
       </c>
       <c r="D8" t="n">
-        <v>16.36968</v>
+        <v>15.47797</v>
       </c>
       <c r="E8" t="n">
-        <v>16.41723</v>
+        <v>16.4402</v>
       </c>
       <c r="F8" t="n">
-        <v>22.01963</v>
+        <v>21.8601</v>
       </c>
       <c r="G8" t="n">
-        <v>34.40871</v>
+        <v>33.94804</v>
       </c>
     </row>
   </sheetData>
